--- a/test/fixtures/deps.xlsx
+++ b/test/fixtures/deps.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U13"/>
+  <dimension ref="A1:U14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1159,6 +1159,59 @@
         <v>3002</v>
       </c>
     </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>600013</v>
+      </c>
+      <c r="B14" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C14" t="n">
+        <v>90</v>
+      </c>
+      <c r="D14" t="n">
+        <v>1003</v>
+      </c>
+      <c r="E14" t="n">
+        <v>31</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>菅野　トキ</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" s="1" t="n">
+        <v>15507</v>
+      </c>
+      <c r="I14" t="n">
+        <v>1</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="n">
+        <v>1</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" t="n">
+        <v>1</v>
+      </c>
+      <c r="N14" t="n">
+        <v>1</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>6500</v>
+      </c>
+      <c r="T14" t="n">
+        <v>3002</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
